--- a/vse-loti/339297386/spec-339297386.xlsx
+++ b/vse-loti/339297386/spec-339297386.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +441,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +512,7 @@
           <t>Поставка стальных труб</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>13.099</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,45 +520,45 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>13.099</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>1120233</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>1344279.6</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>14673932.07</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>1120233</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>1344279.6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="5" t="n">
         <v>13.099</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="6" t="n">
         <v>14673932.07</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="6" t="n">
         <v>1120233</v>
       </c>
     </row>

--- a/vse-loti/339297386/spec-339297386.xlsx
+++ b/vse-loti/339297386/spec-339297386.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -61,16 +62,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,8 +449,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +479,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -520,45 +510,39 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>13.099</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
+        <v>14673932.07</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>1120233</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>1344279.6</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>14673932.07</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>1120233</v>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>1344279.6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>13.099</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>14673932.07</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>1120233</v>
       </c>
     </row>

--- a/vse-loti/339297386/spec-339297386.xlsx
+++ b/vse-loti/339297386/spec-339297386.xlsx
@@ -16,12 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.####"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,12 +30,18 @@
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,7 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,17 +71,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,14 +449,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -499,57 +510,192 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Поставка стальных труб</t>
+          <t>Труба стальная электросварная прямошовная  76х4мм  ГОСТ 10704-91 (Сталь 20 ГОСТ 1050-2013)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46544.33</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>77833.33</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>93400</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная  89х4мм ГОСТ 10704-91 Сталь 20 (Сталь 20 ГОСТ 1050-2013)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>54950.33</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>77833.33</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>93400</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная Ду 108х6мм ГОСТ 10704-91 Сталь 20 (Сталь 20 ГОСТ 1050-2013)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>98848.33</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>77833.33</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>93400</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная 219х8мм ГОСТ 10704-91 Сталь 20 (Сталь 20 ГОСТ 1050-2013)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3.998</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3.998</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>341162.67</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>85333.33</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>102400</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная 325х10мм ГОСТ 10704-91 Сталь 20 (Сталь 20 ГОСТ 1050-2013)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6.527</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6.527</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>578727.33</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>88666.67</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>106400</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="6" t="n">
         <v>13.099</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>13.099</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>14673932.07</v>
-      </c>
-      <c r="G2" s="4" t="n">
+      <c r="F7" s="7" t="n">
         <v>1120233</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>НМЦК (без НДС):</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1120233</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>НМЦК (с НДС):</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>1344279.6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>13.099</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>14673932.07</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>1120233</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Источник: Обоснование НМЦ.xlsx</t>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Источник: Обоснование НМЦ.xlsx (Лист2)</t>
         </is>
       </c>
     </row>
